--- a/rebalanceamentos_template.xlsx
+++ b/rebalanceamentos_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Documentos\Gabriel\Tematica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108F9D9A-C7D6-4110-93CA-246A86ABB1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0CAC9AC-8181-41F8-B03C-1CFD634AF72E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="145">
   <si>
     <t>HISTÓRICO DE REBALANCEAMENTOS — CARTEIRA DE AÇÕES</t>
   </si>
@@ -458,6 +458,18 @@
   </si>
   <si>
     <t>BB Seguridade</t>
+  </si>
+  <si>
+    <t>Eneva</t>
+  </si>
+  <si>
+    <t>ENEV3</t>
+  </si>
+  <si>
+    <t>RADL3</t>
+  </si>
+  <si>
+    <t>Raia Drogasil</t>
   </si>
 </sst>
 </file>
@@ -977,7 +989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1224,8 +1236,12 @@
       <c r="W5" s="8">
         <v>5</v>
       </c>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
+      <c r="X5" s="8">
+        <v>5</v>
+      </c>
+      <c r="Y5" s="8">
+        <v>5</v>
+      </c>
       <c r="Z5" s="9"/>
       <c r="AA5" s="9"/>
       <c r="AB5" s="9"/>
@@ -1301,8 +1317,12 @@
       <c r="W6" s="8">
         <v>5</v>
       </c>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
+      <c r="X6" s="8">
+        <v>5</v>
+      </c>
+      <c r="Y6" s="8">
+        <v>5</v>
+      </c>
       <c r="Z6" s="9"/>
       <c r="AA6" s="9"/>
       <c r="AB6" s="9"/>
@@ -1370,8 +1390,12 @@
       <c r="W7" s="8">
         <v>12</v>
       </c>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
+      <c r="X7" s="8">
+        <v>12</v>
+      </c>
+      <c r="Y7" s="8">
+        <v>5</v>
+      </c>
       <c r="Z7" s="9"/>
       <c r="AA7" s="9"/>
       <c r="AB7" s="9"/>
@@ -1433,8 +1457,12 @@
       <c r="W8" s="8">
         <v>5</v>
       </c>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="9"/>
+      <c r="X8" s="8">
+        <v>5</v>
+      </c>
+      <c r="Y8" s="8">
+        <v>5</v>
+      </c>
       <c r="Z8" s="9"/>
       <c r="AA8" s="9"/>
       <c r="AB8" s="9"/>
@@ -1470,8 +1498,12 @@
       <c r="U9" s="8"/>
       <c r="V9" s="8"/>
       <c r="W9" s="8"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="9"/>
+      <c r="X9" s="8">
+        <v>8</v>
+      </c>
+      <c r="Y9" s="8">
+        <v>10</v>
+      </c>
       <c r="Z9" s="9"/>
       <c r="AA9" s="9"/>
       <c r="AB9" s="9"/>
@@ -1535,8 +1567,12 @@
       <c r="W10" s="8">
         <v>10</v>
       </c>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="9"/>
+      <c r="X10" s="8">
+        <v>10</v>
+      </c>
+      <c r="Y10" s="8">
+        <v>10</v>
+      </c>
       <c r="Z10" s="9"/>
       <c r="AA10" s="9"/>
       <c r="AB10" s="9"/>
@@ -1612,8 +1648,10 @@
       <c r="W11" s="8">
         <v>5</v>
       </c>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
+      <c r="X11" s="8">
+        <v>5</v>
+      </c>
+      <c r="Y11" s="8"/>
       <c r="Z11" s="9"/>
       <c r="AA11" s="9"/>
       <c r="AB11" s="9"/>
@@ -1667,8 +1705,12 @@
       <c r="W12" s="8">
         <v>5</v>
       </c>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
+      <c r="X12" s="8">
+        <v>5</v>
+      </c>
+      <c r="Y12" s="8">
+        <v>5</v>
+      </c>
       <c r="Z12" s="9"/>
       <c r="AA12" s="9"/>
       <c r="AB12" s="9"/>
@@ -1744,8 +1786,12 @@
       <c r="W13" s="8">
         <v>12</v>
       </c>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
+      <c r="X13" s="8">
+        <v>10</v>
+      </c>
+      <c r="Y13" s="8">
+        <v>10</v>
+      </c>
       <c r="Z13" s="9"/>
       <c r="AA13" s="9"/>
       <c r="AB13" s="9"/>
@@ -1795,8 +1841,12 @@
       <c r="W14" s="8">
         <v>12</v>
       </c>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="9"/>
+      <c r="X14" s="8">
+        <v>10</v>
+      </c>
+      <c r="Y14" s="8">
+        <v>10</v>
+      </c>
       <c r="Z14" s="9"/>
       <c r="AA14" s="9"/>
       <c r="AB14" s="9"/>
@@ -1864,8 +1914,12 @@
       <c r="W15" s="8">
         <v>5</v>
       </c>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="9"/>
+      <c r="X15" s="8">
+        <v>5</v>
+      </c>
+      <c r="Y15" s="8">
+        <v>5</v>
+      </c>
       <c r="Z15" s="9"/>
       <c r="AA15" s="9"/>
       <c r="AB15" s="9"/>
@@ -1907,8 +1961,12 @@
       <c r="W16" s="8">
         <v>6</v>
       </c>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="9"/>
+      <c r="X16" s="8">
+        <v>6</v>
+      </c>
+      <c r="Y16" s="8">
+        <v>6</v>
+      </c>
       <c r="Z16" s="9"/>
       <c r="AA16" s="9"/>
       <c r="AB16" s="9"/>
@@ -1944,8 +2002,12 @@
       <c r="U17" s="8"/>
       <c r="V17" s="8"/>
       <c r="W17" s="8"/>
-      <c r="X17" s="9"/>
-      <c r="Y17" s="9"/>
+      <c r="X17" s="8">
+        <v>4</v>
+      </c>
+      <c r="Y17" s="8">
+        <v>10</v>
+      </c>
       <c r="Z17" s="9"/>
       <c r="AA17" s="9"/>
       <c r="AB17" s="9"/>
@@ -2021,8 +2083,12 @@
       <c r="W18" s="8">
         <v>10</v>
       </c>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="9"/>
+      <c r="X18" s="8">
+        <v>10</v>
+      </c>
+      <c r="Y18" s="8">
+        <v>10</v>
+      </c>
       <c r="Z18" s="9"/>
       <c r="AA18" s="9"/>
       <c r="AB18" s="9"/>
@@ -2068,8 +2134,8 @@
       <c r="U19" s="10"/>
       <c r="V19" s="10"/>
       <c r="W19" s="10"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="9"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10"/>
       <c r="Z19" s="9"/>
       <c r="AA19" s="9"/>
       <c r="AB19" s="9"/>
@@ -2125,8 +2191,8 @@
       <c r="U20" s="10"/>
       <c r="V20" s="10"/>
       <c r="W20" s="10"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="9"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="9"/>
       <c r="AB20" s="9"/>
@@ -2200,8 +2266,8 @@
         <v>8</v>
       </c>
       <c r="W21" s="10"/>
-      <c r="X21" s="9"/>
-      <c r="Y21" s="9"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="10"/>
       <c r="Z21" s="9"/>
       <c r="AA21" s="9"/>
       <c r="AB21" s="9"/>
@@ -2249,8 +2315,8 @@
       <c r="U22" s="10"/>
       <c r="V22" s="10"/>
       <c r="W22" s="10"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="9"/>
+      <c r="X22" s="10"/>
+      <c r="Y22" s="10"/>
       <c r="Z22" s="9"/>
       <c r="AA22" s="9"/>
       <c r="AB22" s="9"/>
@@ -2288,8 +2354,8 @@
       <c r="U23" s="10"/>
       <c r="V23" s="10"/>
       <c r="W23" s="10"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="9"/>
+      <c r="X23" s="10"/>
+      <c r="Y23" s="10"/>
       <c r="Z23" s="9"/>
       <c r="AA23" s="9"/>
       <c r="AB23" s="9"/>
@@ -2339,8 +2405,8 @@
       <c r="U24" s="10"/>
       <c r="V24" s="10"/>
       <c r="W24" s="10"/>
-      <c r="X24" s="9"/>
-      <c r="Y24" s="9"/>
+      <c r="X24" s="10"/>
+      <c r="Y24" s="10"/>
       <c r="Z24" s="9"/>
       <c r="AA24" s="9"/>
       <c r="AB24" s="9"/>
@@ -2382,8 +2448,8 @@
       <c r="U25" s="10"/>
       <c r="V25" s="10"/>
       <c r="W25" s="10"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="9"/>
+      <c r="X25" s="10"/>
+      <c r="Y25" s="10"/>
       <c r="Z25" s="9"/>
       <c r="AA25" s="9"/>
       <c r="AB25" s="9"/>
@@ -2443,8 +2509,8 @@
       <c r="U26" s="10"/>
       <c r="V26" s="10"/>
       <c r="W26" s="10"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="9"/>
+      <c r="X26" s="10"/>
+      <c r="Y26" s="10"/>
       <c r="Z26" s="9"/>
       <c r="AA26" s="9"/>
       <c r="AB26" s="9"/>
@@ -2488,8 +2554,8 @@
       <c r="U27" s="10"/>
       <c r="V27" s="10"/>
       <c r="W27" s="10"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
+      <c r="X27" s="10"/>
+      <c r="Y27" s="10"/>
       <c r="Z27" s="9"/>
       <c r="AA27" s="9"/>
       <c r="AB27" s="9"/>
@@ -2527,164 +2593,203 @@
       <c r="W28" s="10">
         <v>8</v>
       </c>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
+      <c r="X28" s="10"/>
+      <c r="Y28" s="10"/>
       <c r="Z28" s="9"/>
       <c r="AA28" s="9"/>
       <c r="AB28" s="9"/>
       <c r="AC28" s="9"/>
     </row>
-    <row r="29" spans="1:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+    <row r="29" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="10"/>
+      <c r="U29" s="10"/>
+      <c r="V29" s="10"/>
+      <c r="W29" s="10"/>
+      <c r="X29" s="10"/>
+      <c r="Y29" s="10">
+        <v>4</v>
+      </c>
+      <c r="Z29" s="9"/>
+      <c r="AA29" s="9"/>
+      <c r="AB29" s="9"/>
+      <c r="AC29" s="9"/>
+    </row>
+    <row r="30" spans="1:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B30" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="14">
-        <f t="shared" ref="D29:AC29" si="0">IFERROR(SUM(D5:D28),"")</f>
-        <v>100</v>
-      </c>
-      <c r="E29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="F29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="G29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="H29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="I29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="J29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="K29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="L29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="M29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="N29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="O29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="P29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="Q29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="R29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="S29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="T29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="U29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="V29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="W29" s="14">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="X29" s="14">
-        <f t="shared" si="0"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="14">
+        <f>IFERROR(SUM(D5:D29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="E30" s="14">
+        <f>IFERROR(SUM(E5:E29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="F30" s="14">
+        <f>IFERROR(SUM(F5:F29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="G30" s="14">
+        <f>IFERROR(SUM(G5:G29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="H30" s="14">
+        <f>IFERROR(SUM(H5:H29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="I30" s="14">
+        <f>IFERROR(SUM(I5:I29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="J30" s="14">
+        <f>IFERROR(SUM(J5:J29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="K30" s="14">
+        <f>IFERROR(SUM(K5:K29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="L30" s="14">
+        <f>IFERROR(SUM(L5:L29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="M30" s="14">
+        <f>IFERROR(SUM(M5:M29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="N30" s="14">
+        <f>IFERROR(SUM(N5:N29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="O30" s="14">
+        <f>IFERROR(SUM(O5:O29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="P30" s="14">
+        <f>IFERROR(SUM(P5:P29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="Q30" s="14">
+        <f>IFERROR(SUM(Q5:Q29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="R30" s="14">
+        <f>IFERROR(SUM(R5:R29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="S30" s="14">
+        <f>IFERROR(SUM(S5:S29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="T30" s="14">
+        <f>IFERROR(SUM(T5:T29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="U30" s="14">
+        <f>IFERROR(SUM(U5:U29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="V30" s="14">
+        <f>IFERROR(SUM(V5:V29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="W30" s="14">
+        <f>IFERROR(SUM(W5:W29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="X30" s="14">
+        <f>IFERROR(SUM(X5:X29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="Y30" s="14">
+        <f t="shared" ref="Y30" si="0">IFERROR(SUM(Y5:Y29),"")</f>
+        <v>100</v>
+      </c>
+      <c r="Z30" s="14">
+        <f>IFERROR(SUM(Z5:Z29),"")</f>
         <v>0</v>
       </c>
-      <c r="Y29" s="14">
-        <f t="shared" si="0"/>
+      <c r="AA30" s="14">
+        <f>IFERROR(SUM(AA5:AA29),"")</f>
         <v>0</v>
       </c>
-      <c r="Z29" s="14">
-        <f t="shared" si="0"/>
+      <c r="AB30" s="14">
+        <f>IFERROR(SUM(AB5:AB29),"")</f>
         <v>0</v>
       </c>
-      <c r="AA29" s="14">
-        <f t="shared" si="0"/>
+      <c r="AC30" s="14">
+        <f>IFERROR(SUM(AC5:AC29),"")</f>
         <v>0</v>
       </c>
-      <c r="AB29" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC29" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
+    </row>
+    <row r="31" spans="1:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
-      <c r="M30" s="18"/>
-      <c r="N30" s="18"/>
-      <c r="O30" s="18"/>
-      <c r="P30" s="18"/>
-      <c r="Q30" s="18"/>
-      <c r="R30" s="18"/>
-      <c r="S30" s="18"/>
-      <c r="T30" s="18"/>
-      <c r="U30" s="18"/>
-      <c r="V30" s="18"/>
-      <c r="W30" s="18"/>
-      <c r="X30" s="18"/>
-      <c r="Y30" s="18"/>
-      <c r="Z30" s="18"/>
-      <c r="AA30" s="18"/>
-      <c r="AB30" s="18"/>
-      <c r="AC30" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="18"/>
+      <c r="R31" s="18"/>
+      <c r="S31" s="18"/>
+      <c r="T31" s="18"/>
+      <c r="U31" s="18"/>
+      <c r="V31" s="18"/>
+      <c r="W31" s="18"/>
+      <c r="X31" s="18"/>
+      <c r="Y31" s="18"/>
+      <c r="Z31" s="18"/>
+      <c r="AA31" s="18"/>
+      <c r="AB31" s="18"/>
+      <c r="AC31" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:AC2"/>
     <mergeCell ref="A1:AC1"/>
-    <mergeCell ref="A30:AC30"/>
+    <mergeCell ref="A31:AC31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2937,8 +3042,12 @@
       <c r="W5" s="8">
         <v>10</v>
       </c>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
+      <c r="X5" s="8">
+        <v>10</v>
+      </c>
+      <c r="Y5" s="8">
+        <v>10</v>
+      </c>
       <c r="Z5" s="9"/>
       <c r="AA5" s="9"/>
       <c r="AB5" s="9"/>
@@ -2994,8 +3103,12 @@
       <c r="W6" s="8">
         <v>5</v>
       </c>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
+      <c r="X6" s="8">
+        <v>8</v>
+      </c>
+      <c r="Y6" s="8">
+        <v>8</v>
+      </c>
       <c r="Z6" s="9"/>
       <c r="AA6" s="9"/>
       <c r="AB6" s="9"/>
@@ -3071,8 +3184,12 @@
       <c r="W7" s="8">
         <v>15</v>
       </c>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
+      <c r="X7" s="8">
+        <v>15</v>
+      </c>
+      <c r="Y7" s="8">
+        <v>5</v>
+      </c>
       <c r="Z7" s="9"/>
       <c r="AA7" s="9"/>
       <c r="AB7" s="9"/>
@@ -3148,8 +3265,12 @@
       <c r="W8" s="8">
         <v>5</v>
       </c>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="9"/>
+      <c r="X8" s="8">
+        <v>5</v>
+      </c>
+      <c r="Y8" s="8">
+        <v>5</v>
+      </c>
       <c r="Z8" s="9"/>
       <c r="AA8" s="9"/>
       <c r="AB8" s="9"/>
@@ -3225,8 +3346,10 @@
       <c r="W9" s="8">
         <v>5</v>
       </c>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="9"/>
+      <c r="X9" s="8">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="8"/>
       <c r="Z9" s="9"/>
       <c r="AA9" s="9"/>
       <c r="AB9" s="9"/>
@@ -3302,8 +3425,12 @@
       <c r="W10" s="8">
         <v>10</v>
       </c>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="9"/>
+      <c r="X10" s="8">
+        <v>10</v>
+      </c>
+      <c r="Y10" s="8">
+        <v>10</v>
+      </c>
       <c r="Z10" s="9"/>
       <c r="AA10" s="9"/>
       <c r="AB10" s="9"/>
@@ -3379,8 +3506,12 @@
       <c r="W11" s="8">
         <v>10</v>
       </c>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
+      <c r="X11" s="8">
+        <v>12</v>
+      </c>
+      <c r="Y11" s="8">
+        <v>15</v>
+      </c>
       <c r="Z11" s="9"/>
       <c r="AA11" s="9"/>
       <c r="AB11" s="9"/>
@@ -3456,8 +3587,12 @@
       <c r="W12" s="8">
         <v>10</v>
       </c>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
+      <c r="X12" s="8">
+        <v>10</v>
+      </c>
+      <c r="Y12" s="8">
+        <v>10</v>
+      </c>
       <c r="Z12" s="9"/>
       <c r="AA12" s="9"/>
       <c r="AB12" s="9"/>
@@ -3521,8 +3656,12 @@
       <c r="W13" s="8">
         <v>10</v>
       </c>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
+      <c r="X13" s="8">
+        <v>15</v>
+      </c>
+      <c r="Y13" s="8">
+        <v>15</v>
+      </c>
       <c r="Z13" s="9"/>
       <c r="AA13" s="9"/>
       <c r="AB13" s="9"/>
@@ -3568,8 +3707,12 @@
       <c r="W14" s="8">
         <v>10</v>
       </c>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="9"/>
+      <c r="X14" s="8">
+        <v>10</v>
+      </c>
+      <c r="Y14" s="8">
+        <v>15</v>
+      </c>
       <c r="Z14" s="9"/>
       <c r="AA14" s="9"/>
       <c r="AB14" s="9"/>
@@ -3645,8 +3788,8 @@
       <c r="W15" s="10">
         <v>10</v>
       </c>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="9"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
       <c r="Z15" s="9"/>
       <c r="AA15" s="9"/>
       <c r="AB15" s="9"/>
@@ -3714,8 +3857,8 @@
       </c>
       <c r="V16" s="10"/>
       <c r="W16" s="10"/>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="9"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="9"/>
       <c r="AB16" s="9"/>
@@ -3763,8 +3906,8 @@
       <c r="U17" s="10"/>
       <c r="V17" s="10"/>
       <c r="W17" s="10"/>
-      <c r="X17" s="9"/>
-      <c r="Y17" s="9"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="10"/>
       <c r="Z17" s="9"/>
       <c r="AA17" s="9"/>
       <c r="AB17" s="9"/>
@@ -3810,17 +3953,23 @@
       <c r="U18" s="10"/>
       <c r="V18" s="10"/>
       <c r="W18" s="10"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="9"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="9"/>
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
     </row>
     <row r="19" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="7"/>
+      <c r="A19" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>142</v>
+      </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
@@ -3841,8 +3990,10 @@
       <c r="U19" s="10"/>
       <c r="V19" s="10"/>
       <c r="W19" s="10"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="9"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10">
+        <v>7</v>
+      </c>
       <c r="Z19" s="9"/>
       <c r="AA19" s="9"/>
       <c r="AB19" s="9"/>
@@ -3937,12 +4088,12 @@
         <v>100</v>
       </c>
       <c r="X20" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="X20:Y20" si="1">IFERROR(SUM(X5:X19),"")</f>
+        <v>100</v>
       </c>
       <c r="Y20" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="Z20" s="14">
         <f t="shared" si="0"/>
